--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487810_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487810_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W. LEVEQUE</t>
+          <t>N. MARINA PARRA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0916</v>
+        <v>2.8046</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0727</v>
+        <v>1.5751</v>
       </c>
       <c r="F2" t="n">
-        <v>0.019</v>
+        <v>1.2294</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3619</v>
+        <v>1.6644</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2516</v>
+        <v>1.8742</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1102</v>
+        <v>-0.2098</v>
       </c>
       <c r="J2" t="n">
-        <v>1.0967</v>
+        <v>1.1093</v>
       </c>
       <c r="K2" t="n">
-        <v>0.313</v>
+        <v>1.7845</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7838000000000001</v>
+        <v>-0.6752</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2651</v>
+        <v>0.5551</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9387</v>
+        <v>0.0897</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6735</v>
+        <v>0.4654</v>
       </c>
       <c r="P2" t="n">
-        <v>1.0406</v>
+        <v>0.4162</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.0406</v>
+        <v>0.4162</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8673</v>
+        <v>0.0163</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4099</v>
+        <v>0.4658</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4574</v>
+        <v>-0.4495</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.1782</v>
+        <v>0.7076</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5661</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.7442</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. MARINA PARRA</t>
+          <t>W. LEVEQUE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.599</v>
+        <v>2.3169</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5751</v>
+        <v>2.6796</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0239</v>
+        <v>-0.3627</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6644</v>
+        <v>1.3619</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8742</v>
+        <v>1.2516</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2098</v>
+        <v>0.1102</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1093</v>
+        <v>1.0967</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7845</v>
+        <v>0.313</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6752</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5551</v>
+        <v>0.2651</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0897</v>
+        <v>0.9387</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4654</v>
+        <v>-0.6735</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4162</v>
+        <v>1.0406</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4162</v>
+        <v>1.0406</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1892</v>
+        <v>1.0926</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4658</v>
+        <v>1.0169</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.655</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7076</v>
+        <v>-1.1782</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7076</v>
+        <v>-1.7442</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. FOREMAN JR</t>
+          <t>A. LAFUENTE SISO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1567</v>
+        <v>1.5677</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5262</v>
+        <v>1.0484</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6304</v>
+        <v>0.5193</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8269</v>
+        <v>1.2511</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0.6698</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1731</v>
+        <v>0.5813</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3374</v>
+        <v>2.0882</v>
       </c>
       <c r="K4" t="n">
-        <v>3.0125</v>
+        <v>1.262</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6752</v>
+        <v>0.8262</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5105</v>
+        <v>-0.8371</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0126</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5021</v>
+        <v>-0.2449</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.0406</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q4" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0406</v>
+        <v>1.8731</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2205</v>
+        <v>-0.4092</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2701</v>
+        <v>-0.1261</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4906</v>
+        <v>-0.2831</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5908</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5908</v>
+        <v>-0.2335</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. GARCIA PEREZ</t>
+          <t>D. FOREMAN JR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8485</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0576</v>
+        <v>0.2048</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9061</v>
+        <v>0.6304</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4394</v>
+        <v>1.8269</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5821</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8572</v>
+        <v>-0.1731</v>
       </c>
       <c r="J5" t="n">
-        <v>0.921</v>
+        <v>2.3374</v>
       </c>
       <c r="K5" t="n">
-        <v>0.921</v>
+        <v>3.0125</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.6752</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5183</v>
+        <v>-0.5105</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3389</v>
+        <v>-1.0126</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8572</v>
+        <v>0.5021</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6649</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q5" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4162</v>
+        <v>1.0406</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7202</v>
+        <v>-0.542</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1025</v>
+        <v>-0.0514</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3823</v>
+        <v>-0.4906</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3538</v>
+        <v>0.5908</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3538</v>
+        <v>0.5908</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. STRIKKER</t>
+          <t>L. GARCIA PEREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.592</v>
+        <v>0.4008</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0778</v>
+        <v>-0.5934</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6698</v>
+        <v>0.9942</v>
       </c>
       <c r="G6" t="n">
-        <v>-5.248</v>
+        <v>1.4394</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.8511</v>
+        <v>0.5821</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3969</v>
+        <v>0.8572</v>
       </c>
       <c r="J6" t="n">
-        <v>-4.8885</v>
+        <v>0.921</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.4508</v>
+        <v>0.921</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4377</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3595</v>
+        <v>0.5183</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4004</v>
+        <v>-0.3389</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0408</v>
+        <v>0.8572</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0406</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0812</v>
+        <v>0.4162</v>
       </c>
       <c r="S6" t="n">
-        <v>3.7487</v>
+        <v>0.2725</v>
       </c>
       <c r="T6" t="n">
-        <v>3.5777</v>
+        <v>0.5668</v>
       </c>
       <c r="U6" t="n">
-        <v>0.171</v>
+        <v>-0.2942</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0508</v>
+        <v>0.3538</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2737</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2229</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LAFUENTE SISO</t>
+          <t>P. MENDES LIMA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2422</v>
+        <v>-0.0086</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1303</v>
+        <v>-1.123</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3725</v>
+        <v>1.1144</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2511</v>
+        <v>0.3694</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6698</v>
+        <v>-1.0896</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5813</v>
+        <v>1.4589</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0882</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>1.262</v>
+        <v>-1.1261</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8262</v>
+        <v>1.2058</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8371</v>
+        <v>0.2897</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5921999999999999</v>
+        <v>0.0366</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2449</v>
+        <v>0.2531</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2081</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8731</v>
+        <v>1.2487</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.7347</v>
+        <v>-0.5963000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.3049</v>
+        <v>-0.2891</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4299</v>
+        <v>-0.3072</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9340000000000001</v>
+        <v>1.0508</v>
       </c>
       <c r="W7" t="n">
         <v>1.1675</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2335</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. MENDES LIMA</t>
+          <t>A. PALAZUELOS PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4372</v>
+        <v>-1.5474</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5516</v>
+        <v>-1.9447</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1144</v>
+        <v>0.3973</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3694</v>
+        <v>-2.8686</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0896</v>
+        <v>-0.9125</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4589</v>
+        <v>-1.9562</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07969999999999999</v>
+        <v>-2.3295</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.1261</v>
+        <v>-0.5121</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2058</v>
+        <v>-1.8174</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2897</v>
+        <v>-0.5391</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0366</v>
+        <v>-0.4004</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2531</v>
+        <v>-0.1388</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.8325</v>
+        <v>1.2487</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1.2487</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0249</v>
+        <v>-0.1716</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7177</v>
+        <v>0.3849</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3072</v>
+        <v>-0.5564</v>
       </c>
       <c r="V8" t="n">
-        <v>1.0508</v>
+        <v>0.2441</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1168</v>
+        <v>0.2441</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SANTOS RODRÍGUEZ</t>
+          <t>M. STRIKKER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0951</v>
+        <v>-1.7566</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0866</v>
+        <v>-3.2209</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0084</v>
+        <v>1.4643</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1131</v>
+        <v>-5.248</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0298</v>
+        <v>-3.8511</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1429</v>
+        <v>-1.3969</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0192</v>
+        <v>-4.8885</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0192</v>
+        <v>-3.4508</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.4377</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0939</v>
+        <v>-0.3595</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.049</v>
+        <v>-0.4004</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1429</v>
+        <v>0.0408</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.0406</v>
+        <v>1.0406</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.0812</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.06519999999999999</v>
+        <v>1.4345</v>
       </c>
       <c r="U9" t="n">
-        <v>0.06519999999999999</v>
+        <v>-0.0345</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1675</v>
+        <v>1.0508</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2737</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1675</v>
+        <v>-0.2229</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. PALAZUELOS PEREZ</t>
+          <t>J. SANTOS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8626</v>
+        <v>-1.9879</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2305</v>
+        <v>-0.9795</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3679</v>
+        <v>-1.0084</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.8686</v>
+        <v>0.1131</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9125</v>
+        <v>-0.0298</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.9562</v>
+        <v>0.1429</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.3295</v>
+        <v>0.0192</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5121</v>
+        <v>0.0192</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8174</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5391</v>
+        <v>0.0939</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4004</v>
+        <v>-0.049</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1388</v>
+        <v>0.1429</v>
       </c>
       <c r="P10" t="n">
-        <v>1.2487</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q10" t="n">
+        <v>-1.0406</v>
+      </c>
+      <c r="R10" t="n">
         <v>0</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.2487</v>
-      </c>
       <c r="S10" t="n">
-        <v>-1.4868</v>
+        <v>0.1072</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.901</v>
+        <v>0.0419</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5858</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2441</v>
+        <v>-1.1675</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2441</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.7132</v>
+        <v>-5.2028</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.1477</v>
+        <v>-5.7546</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4344</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-6.1758</v>
@@ -1312,13 +1312,13 @@
         <v>2.0812</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7014</v>
+        <v>-0.191</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1744</v>
+        <v>0.2187</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5271</v>
+        <v>-0.4096</v>
       </c>
       <c r="V11" t="n">
         <v>1.164</v>
@@ -1348,16 +1348,16 @@
         <v>-2.5781</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.1081</v>
+        <v>-8.1082</v>
       </c>
       <c r="F12" t="n">
-        <v>5.529999999999999</v>
+        <v>5.5301</v>
       </c>
       <c r="G12" t="n">
         <v>-6.2662</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.163899999999999</v>
+        <v>-2.1639</v>
       </c>
       <c r="I12" t="n">
         <v>-4.1027</v>
@@ -1366,7 +1366,7 @@
         <v>-4.8561</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3487000000000002</v>
+        <v>0.3486999999999998</v>
       </c>
       <c r="L12" t="n">
         <v>-5.2048</v>
@@ -1390,13 +1390,13 @@
         <v>11.4465</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9787000000000003</v>
+        <v>0.9784999999999997</v>
       </c>
       <c r="T12" t="n">
-        <v>3.662800000000001</v>
+        <v>3.6629</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.6843</v>
+        <v>-2.6841</v>
       </c>
       <c r="V12" t="n">
         <v>3.7502</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. CORREIA</t>
+          <t>J. JIMÉNEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.0596</v>
+        <v>7.0014</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9696</v>
+        <v>3.5084</v>
       </c>
       <c r="F13" t="n">
-        <v>3.09</v>
+        <v>3.493</v>
       </c>
       <c r="G13" t="n">
-        <v>3.8359</v>
+        <v>3.8714</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7142</v>
+        <v>1.9896</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1217</v>
+        <v>1.8818</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7013</v>
+        <v>3.0186</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5838</v>
+        <v>2.5328</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1176</v>
+        <v>0.4857</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1345</v>
+        <v>0.8529</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1304</v>
+        <v>-0.5432</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0041</v>
+        <v>1.3961</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2081</v>
+        <v>1.0406</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8731</v>
+        <v>2.0812</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7409</v>
+        <v>-0.3696</v>
       </c>
       <c r="T13" t="n">
-        <v>2.6585</v>
+        <v>-0.2209</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0825</v>
+        <v>-0.1487</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.3091</v>
+        <v>2.4589</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.3091</v>
+        <v>1.7513</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ GONZÁLEZ</t>
+          <t>A. BURGOS CABALLERO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.0218</v>
+        <v>5.5027</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4368</v>
+        <v>5.2351</v>
       </c>
       <c r="F14" t="n">
-        <v>3.585</v>
+        <v>0.2676</v>
       </c>
       <c r="G14" t="n">
-        <v>3.8714</v>
+        <v>5.7789</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9896</v>
+        <v>3.9746</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8818</v>
+        <v>1.8043</v>
       </c>
       <c r="J14" t="n">
-        <v>3.0186</v>
+        <v>5.3627</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5328</v>
+        <v>3.9911</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4857</v>
+        <v>1.3716</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8529</v>
+        <v>0.4161</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5432</v>
+        <v>-0.0166</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3961</v>
+        <v>0.4327</v>
       </c>
       <c r="P14" t="n">
-        <v>1.0406</v>
+        <v>0.2081</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0812</v>
+        <v>1.2487</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3491</v>
+        <v>-0.1305</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2925</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0567</v>
+        <v>-0.8135</v>
       </c>
       <c r="V14" t="n">
-        <v>2.4589</v>
+        <v>-0.3538</v>
       </c>
       <c r="W14" t="n">
-        <v>1.7513</v>
+        <v>0.23</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7076</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. BURGOS CABALLERO</t>
+          <t>S. CORREIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.6964</v>
+        <v>3.1722</v>
       </c>
       <c r="E15" t="n">
-        <v>5.6637</v>
+        <v>0.9336</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0327</v>
+        <v>2.2386</v>
       </c>
       <c r="G15" t="n">
-        <v>5.7789</v>
+        <v>3.8359</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9746</v>
+        <v>3.7142</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8043</v>
+        <v>0.1217</v>
       </c>
       <c r="J15" t="n">
-        <v>5.3627</v>
+        <v>3.7013</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9911</v>
+        <v>3.5838</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3716</v>
+        <v>0.1176</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4161</v>
+        <v>0.1345</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0166</v>
+        <v>0.1304</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4327</v>
+        <v>0.0041</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2081</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2487</v>
+        <v>1.8731</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0633</v>
+        <v>0.8535</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1116</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0484</v>
+        <v>0.231</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3538</v>
+        <v>-1.3091</v>
       </c>
       <c r="W15" t="n">
-        <v>0.23</v>
+        <v>-1.3091</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0114</v>
+        <v>-0.0997</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7275</v>
+        <v>-0.8347</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7389</v>
+        <v>0.735</v>
       </c>
       <c r="G16" t="n">
         <v>1.3484</v>
@@ -1702,13 +1702,13 @@
         <v>0.6244</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4736</v>
+        <v>0.3626</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7358</v>
+        <v>0.6287</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2622</v>
+        <v>-0.2661</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3538</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5955</v>
+        <v>-0.6185</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2736</v>
+        <v>-1.3807</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6781</v>
+        <v>0.7622</v>
       </c>
       <c r="G17" t="n">
         <v>-0.8581</v>
@@ -1780,13 +1780,13 @@
         <v>1.2487</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1814</v>
+        <v>0.1584</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1396</v>
+        <v>0.0324</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0418</v>
+        <v>0.1259</v>
       </c>
       <c r="V17" t="n">
         <v>-1.1675</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9745</v>
+        <v>-0.6555</v>
       </c>
       <c r="E18" t="n">
         <v>-1.2336</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2591</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>0.4918</v>
@@ -1858,13 +1858,13 @@
         <v>0.8325</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0907</v>
+        <v>0.2284</v>
       </c>
       <c r="T18" t="n">
         <v>0.1396</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2303</v>
+        <v>0.0888</v>
       </c>
       <c r="V18" t="n">
         <v>-1.1675</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4186</v>
+        <v>-1.4336</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3556</v>
+        <v>-0.6055</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0629</v>
+        <v>-0.8280999999999999</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6585</v>
@@ -1936,13 +1936,13 @@
         <v>0.6244</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3407</v>
+        <v>-0.3557</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.64</v>
+        <v>0.11</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7007</v>
+        <v>-0.4658</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0437</v>
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.5701</v>
+        <v>-2.463</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0376</v>
+        <v>-2.9304</v>
       </c>
       <c r="F20" t="n">
         <v>0.4675</v>
@@ -2014,10 +2014,10 @@
         <v>0.6244</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.261</v>
+        <v>-0.1538</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2701</v>
+        <v>0.3772</v>
       </c>
       <c r="U20" t="n">
         <v>-0.531</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4304</v>
+        <v>-2.5154</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.6655</v>
+        <v>-4.4512</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2351</v>
+        <v>1.9358</v>
       </c>
       <c r="G21" t="n">
         <v>-2.2514</v>
@@ -2092,13 +2092,13 @@
         <v>1.6649</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2435</v>
+        <v>-0.3285</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1866</v>
+        <v>0.0277</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0569</v>
+        <v>-0.3562</v>
       </c>
       <c r="V21" t="n">
         <v>1.5213</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2221</v>
+        <v>-4.5982</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3067</v>
+        <v>-3.771</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9153</v>
+        <v>-0.8272</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5885</v>
@@ -2170,13 +2170,13 @@
         <v>1.6649</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1528</v>
+        <v>-0.529</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2519</v>
+        <v>0.2839</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9009</v>
+        <v>-0.8129</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1051</v>
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>2.577999999999997</v>
+        <v>3.292400000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.529999999999999</v>
+        <v>-5.529999999999998</v>
       </c>
       <c r="F23" t="n">
-        <v>8.1082</v>
+        <v>8.8225</v>
       </c>
       <c r="G23" t="n">
         <v>6.266300000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>2.163900000000001</v>
+        <v>2.163899999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>4.102500000000001</v>
+        <v>4.102499999999999</v>
       </c>
       <c r="J23" t="n">
         <v>1.4102</v>
@@ -2233,7 +2233,7 @@
         <v>4.856100000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3487999999999999</v>
+        <v>-0.3487999999999998</v>
       </c>
       <c r="O23" t="n">
         <v>5.204699999999999</v>
@@ -2248,13 +2248,13 @@
         <v>12.4872</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9786000000000001</v>
+        <v>-0.2642000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>2.6842</v>
+        <v>2.6841</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.6628</v>
+        <v>-2.9485</v>
       </c>
       <c r="V23" t="n">
         <v>-3.7503</v>
